--- a/etf_holdings/2026-10-13_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-10-13_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV21"/>
+  <dimension ref="A1:CF30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,200 +589,250 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
+          <t>00992A_異動類型</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>00992A_調整方向</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>00992A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>00992A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>00992A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>00992A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>00992A_權重變化</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>00992A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>00992A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>00992A_股數變化</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
           <t>00990A_異動類型</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00990A_調整方向</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00990A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00990A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00990A_權重_昨日</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00990A_權重_今日</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00990A_權重變化</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00990A_股數_昨日</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00990A_股數_今日</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00990A_股數變化</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>00405A_異動類型</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>00405A_調整方向</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>00405A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>00405A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>00405A_權重_昨日</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>00405A_權重_今日</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>00405A_權重變化</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>00405A_股數_昨日</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>00405A_股數_今日</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>00405A_股數變化</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>00993A_異動類型</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>00993A_調整方向</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>00993A_權重_昨日</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>00993A_權重_今日</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>00993A_權重變化</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>00993A_股數_昨日</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>00993A_股數_今日</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>00400A_異動類型</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>00400A_調整方向</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>00400A_權重_昨日</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>00400A_權重_今日</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>00400A_權重變化</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>00400A_股數_昨日</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>00400A_股數_今日</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>00400A_股數變化</t>
         </is>
@@ -800,11 +850,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00405A,00985A,00993A</t>
+          <t>00405A,00985A,00992A,00993A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -873,128 +923,174 @@
           <t>69,000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>智邦</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>智邦</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>5.42%</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>5.66%</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>+0.24%</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>1204000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1227000</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>23,000</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>4.42%</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>5.23%</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>+0.81%</t>
         </is>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BJ2" t="n">
         <v>529000</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BK2" t="n">
         <v>609000</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>80,000</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>智邦</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>智邦</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>1.14%</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>1.15%</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>+0.01%</t>
         </is>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BT2" t="n">
         <v>59000</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BU2" t="n">
         <v>56000</v>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>-3,000</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1002,7 +1098,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00400A,00403A,00985A</t>
+          <t>00985A,00992A,00993A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1015,108 +1111,108 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.93%</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1.24%</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>+0.31%</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>200000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>243000</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>43,000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>50000</v>
+        <v>39000</v>
       </c>
       <c r="AG3" t="n">
-        <v>31000</v>
+        <v>54000</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-19,000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>4.48%</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>170000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>176000</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
@@ -1144,55 +1240,65 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="BT3" t="n">
-        <v>39000</v>
+        <v>19000</v>
       </c>
       <c r="BU3" t="n">
-        <v>51000</v>
+        <v>11000</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12,000</t>
-        </is>
-      </c>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1200,111 +1306,111 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00403A,00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>00400A,00403A,00985A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>+0.31%</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>243000</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>43,000</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.56%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>692000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>499000</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-193,000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.58%</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-0.31%</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>350000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>170000</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-180,000</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>-0.94%</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>31000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-19,000</t>
+        </is>
+      </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -1325,52 +1431,16 @@
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>1.10%</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>1.11%</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>47000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>51000</v>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
@@ -1381,24 +1451,70 @@
       <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="inlineStr"/>
       <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>0.85%</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>+0.35%</t>
+        </is>
+      </c>
+      <c r="CD4" t="n">
+        <v>39000</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>51000</v>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00405A,00993A</t>
+          <t>00985A,00992A,00993A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1421,142 +1537,192 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.88%</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1.94%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>102000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>125000</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>23,000</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>63000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>64000</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="n">
-        <v>700000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-695,000</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2.36%</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2.47%</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
         <is>
           <t>+0.11%</t>
         </is>
       </c>
-      <c r="BJ5" t="n">
-        <v>786000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>846000</v>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>60,000</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
+      <c r="BT5" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>46000</v>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00985A,00992A,00993A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1591,50 +1757,86 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>2097000</v>
+        <v>72000</v>
       </c>
       <c r="AG6" t="n">
-        <v>5135000</v>
+        <v>99000</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3,038,000</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+          <t>27,000</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
@@ -1645,80 +1847,90 @@
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>大成鋼</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>大成鋼</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>0.37%</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>810000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>829000</v>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>19,000</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="BT6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>11000</v>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00985A,00992A,00993A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -1748,55 +1960,91 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2.19%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>-1.27%</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>493000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-250,000</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2.78%</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>2.84%</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>39000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>54000</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>15,000</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>255000</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
@@ -1807,148 +2055,194 @@
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2.14%</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>1.12%</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>-1.02%</t>
-        </is>
-      </c>
-      <c r="BJ7" t="n">
-        <v>19000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>11000</v>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>-8,000</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="BT7" t="n">
+        <v>240000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>248000</v>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2.41%</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>2.25%</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>-0.16%</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>2684000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3113000</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>429,000</t>
-        </is>
-      </c>
+          <t>00403A,00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>692000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>499000</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-193,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>350000</v>
+      </c>
+      <c r="W8" t="n">
+        <v>170000</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-180,000</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
@@ -1969,80 +2263,90 @@
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>1.87%</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1345000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1333000</v>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>-12,000</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr"/>
-      <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="BT8" t="n">
+        <v>47000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>51000</v>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00403A,00993A</t>
+          <t>00985A,00992A,00993A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -2055,54 +2359,108 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>0.14%</t>
-        </is>
-      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>800000</v>
-      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>-0.54%</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>128000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>85000</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-43,000</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>3.20%</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>968000</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>986000</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
@@ -2113,72 +2471,82 @@
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>0.43%</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>0.45%</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="BJ9" t="n">
-        <v>184000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>185000</v>
-      </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>3.96%</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>3.89%</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="BT9" t="n">
+        <v>280000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>281000</v>
+      </c>
+      <c r="BV9" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2186,7 +2554,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00400A,00985A</t>
+          <t>00405A,00993A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -2209,52 +2577,16 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2.39%</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>2.21%</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>-0.18%</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>609000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>699000</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>90,000</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
@@ -2275,54 +2607,114 @@
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
+      <c r="BJ10" t="n">
+        <v>700000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>-695,000</t>
+        </is>
+      </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr"/>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr"/>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>2.36%</t>
+        </is>
+      </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr"/>
-      <c r="BT10" t="inlineStr"/>
+          <t>2.47%</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="BT10" t="n">
+        <v>786000</v>
+      </c>
       <c r="BU10" t="n">
-        <v>469000</v>
-      </c>
-      <c r="BV10" t="inlineStr"/>
+        <v>846000</v>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>60,000</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2360,43 +2752,43 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>406000</v>
+        <v>2097000</v>
       </c>
       <c r="AG11" t="n">
-        <v>366000</v>
+        <v>5135000</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-40,000</t>
+          <t>3,038,000</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr"/>
@@ -2419,72 +2811,82 @@
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>1.39%</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="BJ11" t="n">
-        <v>199000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>206000</v>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>7,000</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
-      <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr"/>
-      <c r="BR11" t="inlineStr"/>
-      <c r="BS11" t="inlineStr"/>
-      <c r="BT11" t="inlineStr"/>
-      <c r="BU11" t="inlineStr"/>
-      <c r="BV11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>大成鋼</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>大成鋼</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="BT11" t="n">
+        <v>810000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>829000</v>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>19,000</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2492,7 +2894,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00992A,00993A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2515,62 +2917,62 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>+0.18%</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>310000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>434000</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>124,000</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
+        <v>659000</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>675000</v>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr"/>
@@ -2581,72 +2983,82 @@
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2.98%</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2.93%</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="BJ12" t="n">
-        <v>607000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>577000</v>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>-30,000</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
-      <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
-      <c r="BQ12" t="inlineStr"/>
-      <c r="BR12" t="inlineStr"/>
-      <c r="BS12" t="inlineStr"/>
-      <c r="BT12" t="inlineStr"/>
-      <c r="BU12" t="inlineStr"/>
-      <c r="BV12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="BT12" t="n">
+        <v>214000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>222000</v>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2654,55 +3066,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00981A,00990A</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.88%</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0.43%</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>-0.45%</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>8456450</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4143450</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-4,313,000</t>
-        </is>
-      </c>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -2713,62 +3089,62 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>1.30%</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>-0.51%</t>
-        </is>
-      </c>
-      <c r="AP13" t="n">
-        <v>1665000</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>967000</v>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-698,000</t>
-        </is>
-      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>2.25%</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>2684000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3113000</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>429,000</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
@@ -2789,26 +3165,72 @@
       <c r="BJ13" t="inlineStr"/>
       <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
-      <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr"/>
-      <c r="BQ13" t="inlineStr"/>
-      <c r="BR13" t="inlineStr"/>
-      <c r="BS13" t="inlineStr"/>
-      <c r="BT13" t="inlineStr"/>
-      <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>1.87%</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="BT13" t="n">
+        <v>1345000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1333000</v>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>-12,000</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2816,7 +3238,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00403A,00993A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -2829,62 +3251,44 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>800000</v>
+      </c>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1.94%</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>1.88%</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>102000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>125000</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>23,000</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
@@ -2905,72 +3309,82 @@
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>1.23%</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>1.34%</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>+0.11%</t>
-        </is>
-      </c>
-      <c r="BJ14" t="n">
-        <v>41000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>46000</v>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr"/>
-      <c r="BN14" t="inlineStr"/>
-      <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="BT14" t="n">
+        <v>184000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>185000</v>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2978,7 +3392,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00400A,00985A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -3013,38 +3427,38 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>278000</v>
+        <v>609000</v>
       </c>
       <c r="AG15" t="n">
-        <v>456000</v>
+        <v>699000</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>178,000</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr"/>
@@ -3067,52 +3481,16 @@
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>穩懋</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>穩懋</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>1.07%</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="BJ15" t="n">
-        <v>191000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>204000</v>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>13,000</t>
-        </is>
-      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
       <c r="BM15" t="inlineStr"/>
       <c r="BN15" t="inlineStr"/>
       <c r="BO15" t="inlineStr"/>
@@ -3123,16 +3501,44 @@
       <c r="BT15" t="inlineStr"/>
       <c r="BU15" t="inlineStr"/>
       <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="n">
+        <v>469000</v>
+      </c>
+      <c r="CF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3140,7 +3546,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00992A,00993A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -3163,62 +3569,62 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>3.10%</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>-1.15%</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>300000</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>257000</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-43,000</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="AP16" t="n">
+        <v>422000</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>424000</v>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AU16" t="inlineStr"/>
@@ -3229,72 +3635,82 @@
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>0.94%</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>0.91%</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="BJ16" t="n">
-        <v>58000</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>62000</v>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr"/>
-      <c r="BN16" t="inlineStr"/>
-      <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr"/>
-      <c r="BQ16" t="inlineStr"/>
-      <c r="BR16" t="inlineStr"/>
-      <c r="BS16" t="inlineStr"/>
-      <c r="BT16" t="inlineStr"/>
-      <c r="BU16" t="inlineStr"/>
-      <c r="BV16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="BT16" t="n">
+        <v>22000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>23000</v>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3302,7 +3718,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00985A,00992A</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -3337,49 +3753,67 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>72000</v>
+        <v>126000</v>
       </c>
       <c r="AG17" t="n">
-        <v>99000</v>
+        <v>206000</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>27,000</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
       <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>359000</v>
+      </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
@@ -3391,52 +3825,16 @@
       <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>0.84%</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="BJ17" t="n">
-        <v>13000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>11000</v>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
       <c r="BM17" t="inlineStr"/>
       <c r="BN17" t="inlineStr"/>
       <c r="BO17" t="inlineStr"/>
@@ -3447,16 +3845,26 @@
       <c r="BT17" t="inlineStr"/>
       <c r="BU17" t="inlineStr"/>
       <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3464,7 +3872,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00985A,00992A</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -3494,55 +3902,91 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>493000</v>
+        <v>80000</v>
       </c>
       <c r="AG18" t="n">
-        <v>243000</v>
+        <v>95000</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-250,000</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>6.18%</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>6.32%</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="AP18" t="n">
+        <v>465000</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>475000</v>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr"/>
       <c r="AU18" t="inlineStr"/>
@@ -3553,52 +3997,16 @@
       <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>1.68%</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>1.82%</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>+0.14%</t>
-        </is>
-      </c>
-      <c r="BJ18" t="n">
-        <v>240000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>248000</v>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
       <c r="BM18" t="inlineStr"/>
       <c r="BN18" t="inlineStr"/>
       <c r="BO18" t="inlineStr"/>
@@ -3609,16 +4017,26 @@
       <c r="BT18" t="inlineStr"/>
       <c r="BU18" t="inlineStr"/>
       <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="inlineStr"/>
+      <c r="BX18" t="inlineStr"/>
+      <c r="BY18" t="inlineStr"/>
+      <c r="BZ18" t="inlineStr"/>
+      <c r="CA18" t="inlineStr"/>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr"/>
+      <c r="CD18" t="inlineStr"/>
+      <c r="CE18" t="inlineStr"/>
+      <c r="CF18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3661,38 +4079,38 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>164000</v>
+        <v>406000</v>
       </c>
       <c r="AG19" t="n">
-        <v>128000</v>
+        <v>366000</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-36,000</t>
+          <t>-40,000</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr"/>
@@ -3715,72 +4133,82 @@
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>1.67%</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>+0.28%</t>
-        </is>
-      </c>
-      <c r="BJ19" t="n">
-        <v>114000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>121000</v>
-      </c>
-      <c r="BL19" t="inlineStr">
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="BT19" t="n">
+        <v>199000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>206000</v>
+      </c>
+      <c r="BV19" t="inlineStr">
         <is>
           <t>7,000</t>
         </is>
       </c>
-      <c r="BM19" t="inlineStr"/>
-      <c r="BN19" t="inlineStr"/>
-      <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr"/>
-      <c r="BQ19" t="inlineStr"/>
-      <c r="BR19" t="inlineStr"/>
-      <c r="BS19" t="inlineStr"/>
-      <c r="BT19" t="inlineStr"/>
-      <c r="BU19" t="inlineStr"/>
-      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="inlineStr"/>
+      <c r="CA19" t="inlineStr"/>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr"/>
+      <c r="CD19" t="inlineStr"/>
+      <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3788,55 +4216,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4.78%</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>+0.48%</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>2499000</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2504000</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
+          <t>00992A,00993A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -3857,16 +4249,52 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="AP20" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>158000</v>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
       <c r="AU20" t="inlineStr"/>
@@ -3877,72 +4305,82 @@
       <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="inlineStr"/>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>4.48%</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>+0.31%</t>
-        </is>
-      </c>
-      <c r="BJ20" t="n">
-        <v>79000</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>76000</v>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>-3,000</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr"/>
-      <c r="BN20" t="inlineStr"/>
-      <c r="BO20" t="inlineStr"/>
-      <c r="BP20" t="inlineStr"/>
-      <c r="BQ20" t="inlineStr"/>
-      <c r="BR20" t="inlineStr"/>
-      <c r="BS20" t="inlineStr"/>
-      <c r="BT20" t="inlineStr"/>
-      <c r="BU20" t="inlineStr"/>
-      <c r="BV20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="BT20" t="n">
+        <v>37000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>40000</v>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr"/>
+      <c r="BX20" t="inlineStr"/>
+      <c r="BY20" t="inlineStr"/>
+      <c r="BZ20" t="inlineStr"/>
+      <c r="CA20" t="inlineStr"/>
+      <c r="CB20" t="inlineStr"/>
+      <c r="CC20" t="inlineStr"/>
+      <c r="CD20" t="inlineStr"/>
+      <c r="CE20" t="inlineStr"/>
+      <c r="CF20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3980,43 +4418,43 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>128000</v>
+        <v>310000</v>
       </c>
       <c r="AG21" t="n">
-        <v>85000</v>
+        <v>434000</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-43,000</t>
+          <t>124,000</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr"/>
@@ -4039,62 +4477,1620 @@
       <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="inlineStr"/>
       <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>2.98%</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>2.93%</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="BT21" t="n">
+        <v>607000</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>577000</v>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
+      <c r="BY21" t="inlineStr"/>
+      <c r="BZ21" t="inlineStr"/>
+      <c r="CA21" t="inlineStr"/>
+      <c r="CB21" t="inlineStr"/>
+      <c r="CC21" t="inlineStr"/>
+      <c r="CD21" t="inlineStr"/>
+      <c r="CE21" t="inlineStr"/>
+      <c r="CF21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00981A,00990A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>8456450</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4143450</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-4,313,000</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>-0.51%</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1665000</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>967000</v>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-698,000</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr"/>
+      <c r="BQ22" t="inlineStr"/>
+      <c r="BR22" t="inlineStr"/>
+      <c r="BS22" t="inlineStr"/>
+      <c r="BT22" t="inlineStr"/>
+      <c r="BU22" t="inlineStr"/>
+      <c r="BV22" t="inlineStr"/>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="inlineStr"/>
+      <c r="BZ22" t="inlineStr"/>
+      <c r="CA22" t="inlineStr"/>
+      <c r="CB22" t="inlineStr"/>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00985A,00992A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>-0.95%</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>143000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>126000</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>-17,000</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>3.96%</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>3.89%</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="BJ21" t="n">
-        <v>280000</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>281000</v>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr"/>
-      <c r="BN21" t="inlineStr"/>
-      <c r="BO21" t="inlineStr"/>
-      <c r="BP21" t="inlineStr"/>
-      <c r="BQ21" t="inlineStr"/>
-      <c r="BR21" t="inlineStr"/>
-      <c r="BS21" t="inlineStr"/>
-      <c r="BT21" t="inlineStr"/>
-      <c r="BU21" t="inlineStr"/>
-      <c r="BV21" t="inlineStr"/>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>6.90%</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>6.55%</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="AP23" t="n">
+        <v>871000</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>894000</v>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>23,000</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
+      <c r="BQ23" t="inlineStr"/>
+      <c r="BR23" t="inlineStr"/>
+      <c r="BS23" t="inlineStr"/>
+      <c r="BT23" t="inlineStr"/>
+      <c r="BU23" t="inlineStr"/>
+      <c r="BV23" t="inlineStr"/>
+      <c r="BW23" t="inlineStr"/>
+      <c r="BX23" t="inlineStr"/>
+      <c r="BY23" t="inlineStr"/>
+      <c r="BZ23" t="inlineStr"/>
+      <c r="CA23" t="inlineStr"/>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>+0.32%</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>278000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>456000</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>178,000</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="BT24" t="n">
+        <v>191000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>204000</v>
+      </c>
+      <c r="BV24" t="inlineStr">
+        <is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr"/>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr"/>
+      <c r="CD24" t="inlineStr"/>
+      <c r="CE24" t="inlineStr"/>
+      <c r="CF24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00992A,00993A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="AP25" t="n">
+        <v>844013</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>860013</v>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>4.68%</t>
+        </is>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>4.73%</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="BT25" t="n">
+        <v>446000</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>464000</v>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="inlineStr"/>
+      <c r="CA25" t="inlineStr"/>
+      <c r="CB25" t="inlineStr"/>
+      <c r="CC25" t="inlineStr"/>
+      <c r="CD25" t="inlineStr"/>
+      <c r="CE25" t="inlineStr"/>
+      <c r="CF25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00400A,00992A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>+0.30%</t>
+        </is>
+      </c>
+      <c r="AP26" t="n">
+        <v>164000</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>194000</v>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+      <c r="BO26" t="inlineStr"/>
+      <c r="BP26" t="inlineStr"/>
+      <c r="BQ26" t="inlineStr"/>
+      <c r="BR26" t="inlineStr"/>
+      <c r="BS26" t="inlineStr"/>
+      <c r="BT26" t="inlineStr"/>
+      <c r="BU26" t="inlineStr"/>
+      <c r="BV26" t="inlineStr"/>
+      <c r="BW26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX26" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BY26" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="BZ26" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="CA26" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="CC26" t="inlineStr">
+        <is>
+          <t>-1.22%</t>
+        </is>
+      </c>
+      <c r="CD26" t="n">
+        <v>137000</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>97000</v>
+      </c>
+      <c r="CF26" t="inlineStr">
+        <is>
+          <t>-40,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>-1.15%</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>300000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>257000</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>-43,000</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN27" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO27" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="BP27" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="BQ27" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="BS27" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="BT27" t="n">
+        <v>58000</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>62000</v>
+      </c>
+      <c r="BV27" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="BW27" t="inlineStr"/>
+      <c r="BX27" t="inlineStr"/>
+      <c r="BY27" t="inlineStr"/>
+      <c r="BZ27" t="inlineStr"/>
+      <c r="CA27" t="inlineStr"/>
+      <c r="CB27" t="inlineStr"/>
+      <c r="CC27" t="inlineStr"/>
+      <c r="CD27" t="inlineStr"/>
+      <c r="CE27" t="inlineStr"/>
+      <c r="CF27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>-0.46%</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>164000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>128000</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>-36,000</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN28" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="BP28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="BQ28" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="BS28" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="BT28" t="n">
+        <v>114000</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>121000</v>
+      </c>
+      <c r="BV28" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="BW28" t="inlineStr"/>
+      <c r="BX28" t="inlineStr"/>
+      <c r="BY28" t="inlineStr"/>
+      <c r="BZ28" t="inlineStr"/>
+      <c r="CA28" t="inlineStr"/>
+      <c r="CB28" t="inlineStr"/>
+      <c r="CC28" t="inlineStr"/>
+      <c r="CD28" t="inlineStr"/>
+      <c r="CE28" t="inlineStr"/>
+      <c r="CF28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4.78%</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5.26%</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>2499000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2504000</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN29" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO29" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="BP29" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="BQ29" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>4.48%</t>
+        </is>
+      </c>
+      <c r="BS29" t="inlineStr">
+        <is>
+          <t>+0.31%</t>
+        </is>
+      </c>
+      <c r="BT29" t="n">
+        <v>79000</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>76000</v>
+      </c>
+      <c r="BV29" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="BW29" t="inlineStr"/>
+      <c r="BX29" t="inlineStr"/>
+      <c r="BY29" t="inlineStr"/>
+      <c r="BZ29" t="inlineStr"/>
+      <c r="CA29" t="inlineStr"/>
+      <c r="CB29" t="inlineStr"/>
+      <c r="CC29" t="inlineStr"/>
+      <c r="CD29" t="inlineStr"/>
+      <c r="CE29" t="inlineStr"/>
+      <c r="CF29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00981A,00992A</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3.86%</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>6467000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>6771000</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>304,000</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="AP30" t="n">
+        <v>113000</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>133000</v>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+      <c r="BO30" t="inlineStr"/>
+      <c r="BP30" t="inlineStr"/>
+      <c r="BQ30" t="inlineStr"/>
+      <c r="BR30" t="inlineStr"/>
+      <c r="BS30" t="inlineStr"/>
+      <c r="BT30" t="inlineStr"/>
+      <c r="BU30" t="inlineStr"/>
+      <c r="BV30" t="inlineStr"/>
+      <c r="BW30" t="inlineStr"/>
+      <c r="BX30" t="inlineStr"/>
+      <c r="BY30" t="inlineStr"/>
+      <c r="BZ30" t="inlineStr"/>
+      <c r="CA30" t="inlineStr"/>
+      <c r="CB30" t="inlineStr"/>
+      <c r="CC30" t="inlineStr"/>
+      <c r="CD30" t="inlineStr"/>
+      <c r="CE30" t="inlineStr"/>
+      <c r="CF30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
